--- a/Funding_impactAnalysis/data/HIV_Self_Test_Kits_Subcounty.xlsx
+++ b/Funding_impactAnalysis/data/HIV_Self_Test_Kits_Subcounty.xlsx
@@ -17,7 +17,7 @@
     <t xml:space="preserve">county</t>
   </si>
   <si>
-    <t xml:space="preserve">sub_county</t>
+    <t xml:space="preserve">Sub county</t>
   </si>
   <si>
     <t xml:space="preserve">pre_funding_cut_count_median_IQR</t>
@@ -35,7 +35,7 @@
     <t xml:space="preserve">Baringo County</t>
   </si>
   <si>
-    <t xml:space="preserve">Marigat</t>
+    <t xml:space="preserve">marigat</t>
   </si>
   <si>
     <t xml:space="preserve">0 [0-0]</t>
@@ -50,7 +50,7 @@
     <t xml:space="preserve">Bungoma County</t>
   </si>
   <si>
-    <t xml:space="preserve">Kimilili</t>
+    <t xml:space="preserve">kimilili</t>
   </si>
   <si>
     <t xml:space="preserve">1 [0-1]</t>
@@ -65,13 +65,13 @@
     <t xml:space="preserve">Elgeyo Marakwet County</t>
   </si>
   <si>
-    <t xml:space="preserve">Marakwet West</t>
+    <t xml:space="preserve">marakwet west</t>
   </si>
   <si>
     <t xml:space="preserve">Kiambu County</t>
   </si>
   <si>
-    <t xml:space="preserve">Githunguri</t>
+    <t xml:space="preserve">githunguri</t>
   </si>
   <si>
     <t xml:space="preserve">5 [0-19.17]</t>
@@ -83,7 +83,7 @@
     <t xml:space="preserve">Kilifi County</t>
   </si>
   <si>
-    <t xml:space="preserve">Kaloleni</t>
+    <t xml:space="preserve">kaloleni</t>
   </si>
   <si>
     <t xml:space="preserve">0 [0-12.95]</t>
@@ -92,7 +92,7 @@
     <t xml:space="preserve">10 [0-16.67]</t>
   </si>
   <si>
-    <t xml:space="preserve">Kilifi North</t>
+    <t xml:space="preserve">kilifi north</t>
   </si>
   <si>
     <t xml:space="preserve">1 [0-2]</t>
@@ -107,7 +107,7 @@
     <t xml:space="preserve">Kisii County</t>
   </si>
   <si>
-    <t xml:space="preserve">Nyaribari Chache</t>
+    <t xml:space="preserve">nyaribari chache</t>
   </si>
   <si>
     <t xml:space="preserve">0.5 [0-2]</t>
@@ -119,7 +119,7 @@
     <t xml:space="preserve">Kitui County</t>
   </si>
   <si>
-    <t xml:space="preserve">Kitui East</t>
+    <t xml:space="preserve">kitui east</t>
   </si>
   <si>
     <t xml:space="preserve">0 [0-25]</t>
@@ -131,7 +131,7 @@
     <t xml:space="preserve">Laikipia County</t>
   </si>
   <si>
-    <t xml:space="preserve">Laikipia East</t>
+    <t xml:space="preserve">laikipia east</t>
   </si>
   <si>
     <t xml:space="preserve">10.1 [0-16.67]</t>
@@ -140,13 +140,13 @@
     <t xml:space="preserve">0 [0-7.69]</t>
   </si>
   <si>
-    <t xml:space="preserve">Laikipia North</t>
+    <t xml:space="preserve">laikipia north</t>
   </si>
   <si>
     <t xml:space="preserve">Machakos County</t>
   </si>
   <si>
-    <t xml:space="preserve">Machakos</t>
+    <t xml:space="preserve">machakos</t>
   </si>
   <si>
     <t xml:space="preserve">0.5 [0-1]</t>
@@ -161,13 +161,13 @@
     <t xml:space="preserve">Makueni County</t>
   </si>
   <si>
-    <t xml:space="preserve">Kaiti</t>
+    <t xml:space="preserve">kaiti</t>
   </si>
   <si>
     <t xml:space="preserve">0 [0-0.25]</t>
   </si>
   <si>
-    <t xml:space="preserve">Makueni</t>
+    <t xml:space="preserve">makueni</t>
   </si>
   <si>
     <t xml:space="preserve">0 [0-20.83]</t>
@@ -179,7 +179,7 @@
     <t xml:space="preserve">Mombasa County</t>
   </si>
   <si>
-    <t xml:space="preserve">Jomvu</t>
+    <t xml:space="preserve">jomvu</t>
   </si>
   <si>
     <t xml:space="preserve">0 [0-50]</t>
@@ -188,7 +188,7 @@
     <t xml:space="preserve">0 [0-26.67]</t>
   </si>
   <si>
-    <t xml:space="preserve">Mvita</t>
+    <t xml:space="preserve">mvita</t>
   </si>
   <si>
     <t xml:space="preserve">0 [0-2]</t>
@@ -197,7 +197,7 @@
     <t xml:space="preserve">Nakuru County</t>
   </si>
   <si>
-    <t xml:space="preserve">Naivasha</t>
+    <t xml:space="preserve">naivasha</t>
   </si>
   <si>
     <t xml:space="preserve">1 [0.75-2]</t>
@@ -212,7 +212,7 @@
     <t xml:space="preserve">Nandi County</t>
   </si>
   <si>
-    <t xml:space="preserve">Aldai</t>
+    <t xml:space="preserve">aldai</t>
   </si>
   <si>
     <t xml:space="preserve">0.5 [0-1.25]</t>
@@ -224,7 +224,7 @@
     <t xml:space="preserve">0 [0-10]</t>
   </si>
   <si>
-    <t xml:space="preserve">Emgwen</t>
+    <t xml:space="preserve">emgwen</t>
   </si>
   <si>
     <t xml:space="preserve">4.55 [0-20.56]</t>
@@ -233,7 +233,7 @@
     <t xml:space="preserve">0 [0-2.78]</t>
   </si>
   <si>
-    <t xml:space="preserve">Tinderet</t>
+    <t xml:space="preserve">tinderet</t>
   </si>
   <si>
     <t xml:space="preserve">20.83 [1.92-28.57]</t>
@@ -245,7 +245,7 @@
     <t xml:space="preserve">Narok County</t>
   </si>
   <si>
-    <t xml:space="preserve">Narok Central</t>
+    <t xml:space="preserve">narok central</t>
   </si>
   <si>
     <t xml:space="preserve">0 [0-21.25]</t>
@@ -257,7 +257,7 @@
     <t xml:space="preserve">Nyandarua County</t>
   </si>
   <si>
-    <t xml:space="preserve">Ndaragwa</t>
+    <t xml:space="preserve">ndaragwa</t>
   </si>
   <si>
     <t xml:space="preserve">0 [0-11.67]</t>
@@ -266,22 +266,22 @@
     <t xml:space="preserve">Samburu County</t>
   </si>
   <si>
-    <t xml:space="preserve">Samburu Central</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Samburu East</t>
+    <t xml:space="preserve">samburu central</t>
+  </si>
+  <si>
+    <t xml:space="preserve">samburu east</t>
   </si>
   <si>
     <t xml:space="preserve">0 [0-27.08]</t>
   </si>
   <si>
-    <t xml:space="preserve">Samburu North</t>
+    <t xml:space="preserve">samburu north</t>
   </si>
   <si>
     <t xml:space="preserve">Siaya County</t>
   </si>
   <si>
-    <t xml:space="preserve">Alego Usonga</t>
+    <t xml:space="preserve">alego usonga</t>
   </si>
   <si>
     <t xml:space="preserve">4 [2-6.25]</t>
@@ -296,7 +296,7 @@
     <t xml:space="preserve">8.33 [5-21.43]</t>
   </si>
   <si>
-    <t xml:space="preserve">Bondo</t>
+    <t xml:space="preserve">bondo</t>
   </si>
   <si>
     <t xml:space="preserve">2 [1-4]</t>
@@ -311,7 +311,7 @@
     <t xml:space="preserve">12.5 [7.14-28.57]</t>
   </si>
   <si>
-    <t xml:space="preserve">Gem</t>
+    <t xml:space="preserve">gem</t>
   </si>
   <si>
     <t xml:space="preserve">1.5 [1-4.25]</t>
@@ -326,7 +326,7 @@
     <t xml:space="preserve">15.79 [0-40]</t>
   </si>
   <si>
-    <t xml:space="preserve">Ugenya</t>
+    <t xml:space="preserve">ugenya</t>
   </si>
   <si>
     <t xml:space="preserve">2 [1-3]</t>
@@ -338,7 +338,7 @@
     <t xml:space="preserve">0 [0-27.27]</t>
   </si>
   <si>
-    <t xml:space="preserve">Ugunja</t>
+    <t xml:space="preserve">ugunja</t>
   </si>
   <si>
     <t xml:space="preserve">1 [1-2.25]</t>
@@ -353,7 +353,7 @@
     <t xml:space="preserve">Taita Taveta County</t>
   </si>
   <si>
-    <t xml:space="preserve">Voi</t>
+    <t xml:space="preserve">voi</t>
   </si>
   <si>
     <t xml:space="preserve">7.14 [0-22.5]</t>
@@ -365,19 +365,19 @@
     <t xml:space="preserve">Tharaka Nithi County</t>
   </si>
   <si>
-    <t xml:space="preserve">Maara</t>
+    <t xml:space="preserve">maara</t>
   </si>
   <si>
     <t xml:space="preserve">Turkana County</t>
   </si>
   <si>
-    <t xml:space="preserve">Turkana Central</t>
+    <t xml:space="preserve">turkana central</t>
   </si>
   <si>
     <t xml:space="preserve">25 [0-33.33]</t>
   </si>
   <si>
-    <t xml:space="preserve">Turkana South</t>
+    <t xml:space="preserve">turkana south</t>
   </si>
   <si>
     <t xml:space="preserve">0 [0-40]</t>
@@ -386,7 +386,7 @@
     <t xml:space="preserve">Uasin Gishu County</t>
   </si>
   <si>
-    <t xml:space="preserve">Kapseret</t>
+    <t xml:space="preserve">kapseret</t>
   </si>
   <si>
     <t xml:space="preserve">0 [0-21.11]</t>
@@ -395,10 +395,10 @@
     <t xml:space="preserve">0 [0-16.67]</t>
   </si>
   <si>
-    <t xml:space="preserve">Soy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Turbo</t>
+    <t xml:space="preserve">soy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">turbo</t>
   </si>
   <si>
     <t xml:space="preserve">3.57 [0-11.67]</t>
@@ -407,7 +407,7 @@
     <t xml:space="preserve">Vihiga County</t>
   </si>
   <si>
-    <t xml:space="preserve">Hamisi</t>
+    <t xml:space="preserve">hamisi</t>
   </si>
   <si>
     <t xml:space="preserve">0 [0-1.67]</t>
